--- a/stories/arbres/TREE-DIF-027.xlsx
+++ b/stories/arbres/TREE-DIF-027.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Sara est avec papa, au parc. Sara a envie de jouer. papa est là, tout près. On va apprendre : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara écoute papa. Sara entend les mots : attendre, tendre un jouet, pas forcer la parole.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers la cuisine. Les chaussures font toc toc. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Sara se souvient : attendre, tendre un jouet, pas forcer la parole. Voici le geste : attendre ; tendre le jouet. On dit merci. papa dit : je suis là. On reste ensemble.</t>
+          <t>Sara va vers la cuisine. Les chaussures font toc toc. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Sara se souvient : attendre, tendre un jouet, pas forcer la parole. Voici le geste : attendre ; tendre le jouet. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va vers la cuisine. Les chaussures font toc toc. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Sara se souvient : attendre, tendre un jouet, pas forcer la parole. Voici le geste : attendre ; tendre le jouet. On dit merci.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1858,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Un camarade qui parle peu.</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2031,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : attendre ; tendre le jouet. Sara respire. Sara retient : attendre, tendre un jouet, pas forcer la parole. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2222,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2389,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Sara répète tout bas : attendre, tendre un jouet, pas forcer la parole. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2580,11 @@
         <v>12</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2747,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. Le sol est un peu froid. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le matin. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2914,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3081,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. Une feuille tombe. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3248,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3415,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et le soir. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3582,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3749,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Sara répète tout bas : attendre, tendre un jouet, pas forcer la parole. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3940,11 @@
         <v>12</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4107,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. Une feuille tombe. On dit merci. Cette fin-là est celle de la cuisine, le livre et le matin. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4274,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4441,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et après la sieste. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4608,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4775,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et le soir. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4942,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5109,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Sara répète tout bas : attendre, tendre un jouet, pas forcer la parole. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5300,11 @@
         <v>12</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5467,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le matin. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5634,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5801,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5968,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6135,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et le soir. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6302,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6163,7 +6331,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers le jardin. La couverture est douce. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Sara se souvient : attendre, tendre un jouet, pas forcer la parole. Voici le geste : attendre ; tendre le jouet. On souffle doucement. papa dit : je suis là. On reste ensemble.</t>
+          <t>Sara va vers le jardin. La couverture est douce. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Sara se souvient : attendre, tendre un jouet, pas forcer la parole. Voici le geste : attendre ; tendre le jouet. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6301,6 +6469,12 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va vers le jardin. La couverture est douce. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Sara se souvient : attendre, tendre un jouet, pas forcer la parole. Voici le geste : attendre ; tendre le jouet. On souffle doucement.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6651,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Un camarade qui parle peu.</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6824,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : attendre ; tendre le jouet. Sara respire. Sara retient : attendre, tendre un jouet, pas forcer la parole. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6831,6 +7015,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6993,6 +7182,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi les cubes. Le sol est un peu froid. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Sara répète tout bas : attendre, tendre un jouet, pas forcer la parole. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7179,6 +7373,11 @@
         <v>12</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7341,6 +7540,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le matin. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7503,6 +7707,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7665,6 +7874,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et après la sieste. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7827,6 +8041,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7989,6 +8208,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le jardin, les cubes et le soir. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8151,6 +8375,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8313,6 +8542,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le livre. Une feuille tombe. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Sara répète tout bas : attendre, tendre un jouet, pas forcer la parole. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8499,6 +8733,11 @@
         <v>12</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8661,6 +8900,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le matin. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8823,6 +9067,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8985,6 +9234,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et après la sieste. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9147,6 +9401,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9309,6 +9568,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. La lumière est claire. On attend son tour. Cette fin-là est celle de le jardin, le livre et le soir. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9471,6 +9735,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9633,6 +9902,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi la dînette. L'eau coule, tout petit bruit. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Sara répète tout bas : attendre, tendre un jouet, pas forcer la parole. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9819,6 +10093,11 @@
         <v>12</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9981,6 +10260,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le matin. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10143,6 +10427,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10305,6 +10594,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et après la sieste. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10467,6 +10761,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10629,6 +10928,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le jardin, la dînette et le soir. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10791,6 +11095,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10815,7 +11124,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers la chambre. On entend un oiseau. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Sara se souvient : attendre, tendre un jouet, pas forcer la parole. Voici le geste : attendre ; tendre le jouet. On écoute jusqu'au bout. papa dit : je suis là. On reste ensemble.</t>
+          <t>Sara va vers la chambre. On entend un oiseau. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Sara se souvient : attendre, tendre un jouet, pas forcer la parole. Voici le geste : attendre ; tendre le jouet. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10953,6 +11262,12 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va vers la chambre. On entend un oiseau. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Sara se souvient : attendre, tendre un jouet, pas forcer la parole. Voici le geste : attendre ; tendre le jouet. On écoute jusqu'au bout.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11129,6 +11444,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Un camarade qui parle peu.</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11617,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : attendre ; tendre le jouet. Sara respire. Sara retient : attendre, tendre un jouet, pas forcer la parole. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11483,6 +11808,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11645,6 +11975,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Sara répète tout bas : attendre, tendre un jouet, pas forcer la parole. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11831,6 +12166,11 @@
         <v>12</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11993,6 +12333,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le matin. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12155,6 +12500,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12317,6 +12667,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de la chambre, les cubes et après la sieste. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12479,6 +12834,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12641,6 +13001,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et le soir. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12803,6 +13168,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12965,6 +13335,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Sara répète tout bas : attendre, tendre un jouet, pas forcer la parole. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13151,6 +13526,11 @@
         <v>12</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13313,6 +13693,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le matin. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13475,6 +13860,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13637,6 +14027,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. La lumière est claire. On attend son tour. Cette fin-là est celle de la chambre, le livre et après la sieste. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13799,6 +14194,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13961,6 +14361,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et le soir. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14123,6 +14528,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14285,6 +14695,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Sara répète tout bas : attendre, tendre un jouet, pas forcer la parole. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14471,6 +14886,11 @@
         <v>12</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14633,6 +15053,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le matin. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le matin. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14795,6 +15220,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14957,6 +15387,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint après la sieste. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de la chambre, la dînette et après la sieste. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15119,6 +15554,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15281,6 +15721,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint le soir. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et le soir. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15443,6 +15888,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15461,7 +15911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15478,6 +15928,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-DIF-027.xlsx
+++ b/stories/arbres/TREE-DIF-027.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,11 @@
           <t>narrateur|Aujourd'hui, Sara est avec papa, au parc. Sara a envie de jouer. papa est là, tout près. On va apprendre : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara écoute papa. Sara entend les mots : attendre, tendre un jouet, pas forcer la parole.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1524,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1693,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1865,6 +1877,7 @@
           <t>narrateur|Que fait-on ? Un camarade qui parle peu.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2036,6 +2049,7 @@
           <t>narrateur|Oui. Voici le geste : attendre ; tendre le jouet. Sara respire. Sara retient : attendre, tendre un jouet, pas forcer la parole. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2227,6 +2241,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2394,6 +2409,7 @@
           <t>narrateur|Sara a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Sara répète tout bas : attendre, tendre un jouet, pas forcer la parole. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2585,6 +2601,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2752,6 +2769,7 @@
           <t>narrateur|Sara rejoint le matin. Le sol est un peu froid. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le matin. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2919,6 +2937,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3086,6 +3105,7 @@
           <t>narrateur|Sara rejoint après la sieste. Une feuille tombe. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3253,6 +3273,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3420,6 +3441,7 @@
           <t>narrateur|Sara rejoint le soir. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et le soir. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3587,6 +3609,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3754,6 +3777,7 @@
           <t>narrateur|Sara a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Sara répète tout bas : attendre, tendre un jouet, pas forcer la parole. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3945,6 +3969,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4112,6 +4137,7 @@
           <t>narrateur|Sara rejoint le matin. Une feuille tombe. On dit merci. Cette fin-là est celle de la cuisine, le livre et le matin. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4279,6 +4305,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4446,6 +4473,7 @@
           <t>narrateur|Sara rejoint après la sieste. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et après la sieste. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4613,6 +4641,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4780,6 +4809,7 @@
           <t>narrateur|Sara rejoint le soir. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et le soir. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4947,6 +4977,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5114,6 +5145,7 @@
           <t>narrateur|Sara a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Sara répète tout bas : attendre, tendre un jouet, pas forcer la parole. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5305,6 +5337,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5472,6 +5505,7 @@
           <t>narrateur|Sara rejoint le matin. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le matin. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5639,6 +5673,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5806,6 +5841,7 @@
           <t>narrateur|Sara rejoint après la sieste. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5973,6 +6009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6140,6 +6177,7 @@
           <t>narrateur|Sara rejoint le soir. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et le soir. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6307,6 +6345,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6475,6 +6514,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6658,6 +6698,7 @@
           <t>narrateur|Que fait-on ? Un camarade qui parle peu.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6829,6 +6870,7 @@
           <t>narrateur|Oui. Voici le geste : attendre ; tendre le jouet. Sara respire. Sara retient : attendre, tendre un jouet, pas forcer la parole. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7020,6 +7062,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7187,6 +7230,7 @@
           <t>narrateur|Sara a choisi les cubes. Le sol est un peu froid. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Sara répète tout bas : attendre, tendre un jouet, pas forcer la parole. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7378,6 +7422,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7545,6 +7590,7 @@
           <t>narrateur|Sara rejoint le matin. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le matin. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7712,6 +7758,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7879,6 +7926,7 @@
           <t>narrateur|Sara rejoint après la sieste. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et après la sieste. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8046,6 +8094,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8213,6 +8262,7 @@
           <t>narrateur|Sara rejoint le soir. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le jardin, les cubes et le soir. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8380,6 +8430,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8547,6 +8598,7 @@
           <t>narrateur|Sara a choisi le livre. Une feuille tombe. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Sara répète tout bas : attendre, tendre un jouet, pas forcer la parole. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8738,6 +8790,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8905,6 +8958,7 @@
           <t>narrateur|Sara rejoint le matin. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le matin. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9072,6 +9126,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9239,6 +9294,7 @@
           <t>narrateur|Sara rejoint après la sieste. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et après la sieste. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9406,6 +9462,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9573,6 +9630,7 @@
           <t>narrateur|Sara rejoint le soir. La lumière est claire. On attend son tour. Cette fin-là est celle de le jardin, le livre et le soir. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9740,6 +9798,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9907,6 +9966,7 @@
           <t>narrateur|Sara a choisi la dînette. L'eau coule, tout petit bruit. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Sara répète tout bas : attendre, tendre un jouet, pas forcer la parole. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10098,6 +10158,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10265,6 +10326,7 @@
           <t>narrateur|Sara rejoint le matin. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le matin. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10432,6 +10494,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10599,6 +10662,7 @@
           <t>narrateur|Sara rejoint après la sieste. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et après la sieste. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10766,6 +10830,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10933,6 +10998,7 @@
           <t>narrateur|Sara rejoint le soir. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le jardin, la dînette et le soir. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11100,6 +11166,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11268,6 +11335,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11451,6 +11519,7 @@
           <t>narrateur|Que fait-on ? Un camarade qui parle peu.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11622,6 +11691,7 @@
           <t>narrateur|Oui. Voici le geste : attendre ; tendre le jouet. Sara respire. Sara retient : attendre, tendre un jouet, pas forcer la parole. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11813,6 +11883,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11980,6 +12051,7 @@
           <t>narrateur|Sara a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Sara répète tout bas : attendre, tendre un jouet, pas forcer la parole. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12171,6 +12243,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12338,6 +12411,7 @@
           <t>narrateur|Sara rejoint le matin. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le matin. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12505,6 +12579,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12672,6 +12747,7 @@
           <t>narrateur|Sara rejoint après la sieste. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de la chambre, les cubes et après la sieste. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12839,6 +12915,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13006,6 +13083,7 @@
           <t>narrateur|Sara rejoint le soir. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et le soir. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13173,6 +13251,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13340,6 +13419,7 @@
           <t>narrateur|Sara a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Sara répète tout bas : attendre, tendre un jouet, pas forcer la parole. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13531,6 +13611,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13698,6 +13779,7 @@
           <t>narrateur|Sara rejoint le matin. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le matin. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13865,6 +13947,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14032,6 +14115,7 @@
           <t>narrateur|Sara rejoint après la sieste. La lumière est claire. On attend son tour. Cette fin-là est celle de la chambre, le livre et après la sieste. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14199,6 +14283,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14366,6 +14451,7 @@
           <t>narrateur|Sara rejoint le soir. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et le soir. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14533,6 +14619,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14700,6 +14787,7 @@
           <t>narrateur|Sara a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : attendre ; tendre le jouet. Sara répète tout bas : attendre, tendre un jouet, pas forcer la parole. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14891,6 +14979,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15058,6 +15147,7 @@
           <t>narrateur|Sara rejoint le matin. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le matin. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15225,6 +15315,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15392,6 +15483,7 @@
           <t>narrateur|Sara rejoint après la sieste. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de la chambre, la dînette et après la sieste. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15559,6 +15651,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15726,6 +15819,7 @@
           <t>narrateur|Sara rejoint le soir. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et le soir. Sara a appris : Un camarade qui parle peu. Voici le geste : attendre ; tendre le jouet. Sara a entendu : attendre, tendre un jouet, pas forcer la parole. Sara dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15893,6 +15987,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15911,7 +16006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15935,6 +16030,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15949,7 +16058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16136,6 +16245,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-DIF-027.xlsx
+++ b/stories/arbres/TREE-DIF-027.xlsx
@@ -1383,12 +1383,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le panier reste ouvert, près des pieds. La cuillère, la clochette, et la ficelle. Tu prends quoi d'abord, Sarah ?</t>
+          <t>Le panier reste ouvert, près des pieds. Une cuillère y brille, encore tiède. Une clochette, puis une ficelle, à côté. Tu prends quoi d'abord, Sarah ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Le panier reste ouvert, près des pieds. La cuillère, la clochette, et la ficelle. Tu prends quoi d'abord, Sarah ?</t>
+          <t>Le panier reste ouvert, près des pieds. Une cuillère y brille, encore tiède. Une clochette, puis une ficelle, à côté. Tu prends quoi d'abord, Sarah ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1548,7 +1548,8 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|Le panier reste ouvert, près des pieds.
-narrateur|La cuillère, la clochette, et la ficelle.
+narrateur|Une cuillère y brille, encore tiède.
+narrateur|Une clochette, puis une ficelle, à côté.
 papa|Tu prends quoi d'abord, Sarah ?</t>
         </is>
       </c>
@@ -1576,12 +1577,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah prend d'abord la cuillère chaude. Elle sent le savon. Le métal est encore un peu mouillé. Elle la tend vers Aniss, tout près. Dis ding ! Aniss pose un doigt sur le creux. Ça fait un tout petit tic. La clochette et la ficelle viennent aussi. Papa glisse le tout dans le panier. Les trois affaires restent ensemble. Aniss, on part ? Aniss hoche la tête, tout petit. La cuillère d'abord, vous l'avez.</t>
+          <t>Sarah prend d'abord la cuillère chaude. Elle sent le savon. Le métal est encore un peu mouillé. Elle la tend vers Aniss, tout près. Dis ding ! Aniss pose un doigt sur le creux. Ça fait un tout petit tic. La clochette et la ficelle viennent aussi. Papa glisse le tout dans le panier. Rien ne reste sur la table. Aniss, on part ? Aniss hoche la tête, tout petit. La cuillère d'abord, vous l'avez.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Sarah prend d'abord la cuillère chaude. Elle sent le savon. Le métal est encore un peu mouillé. Elle la tend vers Aniss, tout près. Dis ding ! Aniss pose un doigt sur le creux. Ça fait un tout petit tic. La clochette et la ficelle viennent aussi. Papa glisse le tout dans le panier. Les trois affaires restent ensemble. Aniss, on part ? Aniss hoche la tête, tout petit. La cuillère d'abord, vous l'avez.</t>
+          <t>Sarah prend d'abord la cuillère chaude. Elle sent le savon. Le métal est encore un peu mouillé. Elle la tend vers Aniss, tout près. Dis ding ! Aniss pose un doigt sur le creux. Ça fait un tout petit tic. La clochette et la ficelle viennent aussi. Papa glisse le tout dans le panier. Rien ne reste sur la table. Aniss, on part ? Aniss hoche la tête, tout petit. La cuillère d'abord, vous l'avez.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1725,7 +1726,7 @@
 narrateur|Ça fait un tout petit tic.
 maman|La clochette et la ficelle viennent aussi.
 narrateur|Papa glisse le tout dans le panier.
-narrateur|Les trois affaires restent ensemble.
+narrateur|Rien ne reste sur la table.
 enfant-f|Aniss, on part ?
 narrateur|Aniss hoche la tête, tout petit.
 papa|La cuillère d'abord, vous l'avez.</t>
@@ -2116,12 +2117,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>La cuillère voyage déjà dans le panier. Sous l'étendoir, un linge pend, encore mouillé. Sur la poutre, un clou brille, trop haut. Sur la marche, le vent pousse déjà. On commence où, pour le fil ?</t>
+          <t>La cuillère voyage déjà dans le panier. Dehors, le fil peut aller en trois coins. Un linge mouillé barre encore l'étendoir. Plus haut, un clou attend sur la poutre. Plus bas, le vent pousse la marche. On commence où, pour le fil ?</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>La cuillère voyage déjà dans le panier. Sous l'étendoir, un linge pend, encore mouillé. Sur la poutre, un clou brille, trop haut. Sur la marche, le vent pousse déjà. On commence où, pour le fil ?</t>
+          <t>La cuillère voyage déjà dans le panier. Dehors, le fil peut aller en trois coins. Un linge mouillé barre encore l'étendoir. Plus haut, un clou attend sur la poutre. Plus bas, le vent pousse la marche. On commence où, pour le fil ?</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2281,9 +2282,10 @@
       <c r="AW7" t="inlineStr">
         <is>
           <t>narrateur|La cuillère voyage déjà dans le panier.
-narrateur|Sous l'étendoir, un linge pend, encore mouillé.
-narrateur|Sur la poutre, un clou brille, trop haut.
-narrateur|Sur la marche, le vent pousse déjà.
+narrateur|Dehors, le fil peut aller en trois coins.
+narrateur|Un linge mouillé barre encore l'étendoir.
+narrateur|Plus haut, un clou attend sur la poutre.
+narrateur|Plus bas, le vent pousse la marche.
 papa|On commence où, pour le fil ?</t>
         </is>
       </c>
@@ -3028,12 +3030,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Pour toi. Sarah tend la cuillère vers Aniss. Aniss lève le torchon avec la cuillère. Le bois redevient libre, tout doux. Il passe ! Le fil a pris le bord, tout seul. Le métal a trouvé le linge. La cuillère reste un instant sur le bois.</t>
+          <t>Pour toi. Sarah tend la cuillère vers Aniss. Aniss lève le torchon avec la cuillère. La cuillère attend près du bois, déjà. Le bois redevient libre, tout doux. Il passe ! Le fil a pris le bord, tout seul. Le métal a trouvé le linge.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Pour toi. Sarah tend la cuillère vers Aniss. Aniss lève le torchon avec la cuillère. Le bois redevient libre, tout doux. Il passe ! Le fil a pris le bord, tout seul. Le métal a trouvé le linge. La cuillère reste un instant sur le bois.</t>
+          <t>Pour toi. Sarah tend la cuillère vers Aniss. Aniss lève le torchon avec la cuillère. La cuillère attend près du bois, déjà. Le bois redevient libre, tout doux. Il passe ! Le fil a pris le bord, tout seul. Le métal a trouvé le linge.</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3171,11 +3173,11 @@
           <t>enfant-f|Pour toi.
 narrateur|Sarah tend la cuillère vers Aniss.
 narrateur|Aniss lève le torchon avec la cuillère.
+narrateur|La cuillère attend près du bois, déjà.
 narrateur|Le bois redevient libre, tout doux.
 enfant-f|Il passe !
 maman|Le fil a pris le bord, tout seul.
-papa|Le métal a trouvé le linge.
-narrateur|La cuillère reste un instant sur le bois.</t>
+papa|Le métal a trouvé le linge.</t>
         </is>
       </c>
     </row>
@@ -6547,12 +6549,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sarah prend d'abord la clochette froide. Elle va tinter. Le métal est un peu rêche. Elle la tend vers Aniss. Dis ding ! Aniss la tient à deux mains. Ça tinte une fois, puis s'arrête. La cuillère et la ficelle viennent aussi. Maman les pose près du panier. Les trois affaires restent ensemble. Aniss, tu viens ? Aniss lève la clochette, tout bas. La clochette d'abord, vous l'avez.</t>
+          <t>Sarah prend d'abord la clochette froide. Elle va tinter. Le métal est un peu rêche. Elle la tend vers Aniss. Dis ding ! Aniss la tient à deux mains. Ça tinte une fois, puis s'arrête. La cuillère et la ficelle viennent aussi. Maman les pose près du panier. Tout part ensemble, déjà. Aniss, tu viens ? Aniss lève la clochette, tout bas. La clochette d'abord, vous l'avez.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Sarah prend d'abord la clochette froide. Elle va tinter. Le métal est un peu rêche. Elle la tend vers Aniss. Dis ding ! Aniss la tient à deux mains. Ça tinte une fois, puis s'arrête. La cuillère et la ficelle viennent aussi. Maman les pose près du panier. Les trois affaires restent ensemble. Aniss, tu viens ? Aniss lève la clochette, tout bas. La clochette d'abord, vous l'avez.</t>
+          <t>Sarah prend d'abord la clochette froide. Elle va tinter. Le métal est un peu rêche. Elle la tend vers Aniss. Dis ding ! Aniss la tient à deux mains. Ça tinte une fois, puis s'arrête. La cuillère et la ficelle viennent aussi. Maman les pose près du panier. Tout part ensemble, déjà. Aniss, tu viens ? Aniss lève la clochette, tout bas. La clochette d'abord, vous l'avez.</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -6696,7 +6698,7 @@
 narrateur|Ça tinte une fois, puis s'arrête.
 papa|La cuillère et la ficelle viennent aussi.
 narrateur|Maman les pose près du panier.
-narrateur|Les trois affaires restent ensemble.
+narrateur|Tout part ensemble, déjà.
 enfant-f|Aniss, tu viens ?
 narrateur|Aniss lève la clochette, tout bas.
 maman|La clochette d'abord, vous l'avez.</t>
@@ -7087,12 +7089,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>La clochette voyage déjà dans le panier. Sous l'étendoir, un linge pend, encore mouillé. Sur la poutre, un clou brille, trop haut. Sur la marche, le vent pousse déjà. On commence où, pour le fil ?</t>
+          <t>La clochette voyage déjà dans le panier. Dehors, le fil peut aller en trois coins. Un linge mouillé barre encore l'étendoir. Plus haut, un clou attend sur la poutre. Plus bas, le vent pousse la marche. On commence où, pour le fil ?</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>La clochette voyage déjà dans le panier. Sous l'étendoir, un linge pend, encore mouillé. Sur la poutre, un clou brille, trop haut. Sur la marche, le vent pousse déjà. On commence où, pour le fil ?</t>
+          <t>La clochette voyage déjà dans le panier. Dehors, le fil peut aller en trois coins. Un linge mouillé barre encore l'étendoir. Plus haut, un clou attend sur la poutre. Plus bas, le vent pousse la marche. On commence où, pour le fil ?</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -7252,9 +7254,10 @@
       <c r="AW35" t="inlineStr">
         <is>
           <t>narrateur|La clochette voyage déjà dans le panier.
-narrateur|Sous l'étendoir, un linge pend, encore mouillé.
-narrateur|Sur la poutre, un clou brille, trop haut.
-narrateur|Sur la marche, le vent pousse déjà.
+narrateur|Dehors, le fil peut aller en trois coins.
+narrateur|Un linge mouillé barre encore l'étendoir.
+narrateur|Plus haut, un clou attend sur la poutre.
+narrateur|Plus bas, le vent pousse la marche.
 papa|On commence où, pour le fil ?</t>
         </is>
       </c>
@@ -7999,12 +8002,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Pour toi. Sarah tend la cuillère vers Aniss. Aniss lève le torchon avec la clochette. Le bois redevient libre, tout doux. Il passe ! Le fil a pris le bord, tout seul. Le métal a trouvé le linge. La clochette reste un instant sur le bois.</t>
+          <t>Pour toi. Sarah tend la cuillère vers Aniss. Aniss lève le torchon avec la cuillère. La clochette attend près du bois, déjà. Le bois redevient libre, tout doux. Il passe ! Le fil a pris le bord, tout seul. Le métal a trouvé le linge.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Pour toi. Sarah tend la cuillère vers Aniss. Aniss lève le torchon avec la clochette. Le bois redevient libre, tout doux. Il passe ! Le fil a pris le bord, tout seul. Le métal a trouvé le linge. La clochette reste un instant sur le bois.</t>
+          <t>Pour toi. Sarah tend la cuillère vers Aniss. Aniss lève le torchon avec la cuillère. La clochette attend près du bois, déjà. Le bois redevient libre, tout doux. Il passe ! Le fil a pris le bord, tout seul. Le métal a trouvé le linge.</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -8141,12 +8144,12 @@
         <is>
           <t>enfant-f|Pour toi.
 narrateur|Sarah tend la cuillère vers Aniss.
-narrateur|Aniss lève le torchon avec la clochette.
+narrateur|Aniss lève le torchon avec la cuillère.
+narrateur|La clochette attend près du bois, déjà.
 narrateur|Le bois redevient libre, tout doux.
 enfant-f|Il passe !
 maman|Le fil a pris le bord, tout seul.
-papa|Le métal a trouvé le linge.
-narrateur|La clochette reste un instant sur le bois.</t>
+papa|Le métal a trouvé le linge.</t>
         </is>
       </c>
     </row>
@@ -11518,12 +11521,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sarah prend d'abord la ficelle douce. C'est pour le fil. Elle sent encore le tiroir. Elle tend le peloton vers Aniss. Dis fil ! Aniss enroule un bout, tout lent. Le fil se fait, sans un mot. La cuillère et la clochette viennent aussi. Papa les glisse près du sac. Les trois affaires restent ensemble. Aniss, c'est bon ? Aniss appuie sur le fil, tout calme. La ficelle d'abord, elle tient.</t>
+          <t>Sarah prend d'abord la ficelle douce. C'est pour le fil. Elle sent encore le tiroir. Elle tend le peloton vers Aniss. Dis fil ! Aniss enroule un bout, tout lent. Le fil se fait, sans un mot. La cuillère et la clochette viennent aussi. Papa les glisse près du sac. Le panier les garde, toutes les trois. Aniss, c'est bon ? Aniss appuie sur le fil, tout calme. La ficelle d'abord, elle tient.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Sarah prend d'abord la ficelle douce. C'est pour le fil. Elle sent encore le tiroir. Elle tend le peloton vers Aniss. Dis fil ! Aniss enroule un bout, tout lent. Le fil se fait, sans un mot. La cuillère et la clochette viennent aussi. Papa les glisse près du sac. Les trois affaires restent ensemble. Aniss, c'est bon ? Aniss appuie sur le fil, tout calme. La ficelle d'abord, elle tient.</t>
+          <t>Sarah prend d'abord la ficelle douce. C'est pour le fil. Elle sent encore le tiroir. Elle tend le peloton vers Aniss. Dis fil ! Aniss enroule un bout, tout lent. Le fil se fait, sans un mot. La cuillère et la clochette viennent aussi. Papa les glisse près du sac. Le panier les garde, toutes les trois. Aniss, c'est bon ? Aniss appuie sur le fil, tout calme. La ficelle d'abord, elle tient.</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -11667,7 +11670,7 @@
 narrateur|Le fil se fait, sans un mot.
 maman|La cuillère et la clochette viennent aussi.
 narrateur|Papa les glisse près du sac.
-narrateur|Les trois affaires restent ensemble.
+narrateur|Le panier les garde, toutes les trois.
 enfant-f|Aniss, c'est bon ?
 narrateur|Aniss appuie sur le fil, tout calme.
 papa|La ficelle d'abord, elle tient.</t>
@@ -12058,12 +12061,12 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>La ficelle voyage déjà dans le panier. Sous l'étendoir, un linge pend, encore mouillé. Sur la poutre, un clou brille, trop haut. Sur la marche, le vent pousse déjà. On commence où, pour le fil ?</t>
+          <t>La ficelle voyage déjà dans le panier. Dehors, le fil peut aller en trois coins. Un linge mouillé barre encore l'étendoir. Plus haut, un clou attend sur la poutre. Plus bas, le vent pousse la marche. On commence où, pour le fil ?</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>La ficelle voyage déjà dans le panier. Sous l'étendoir, un linge pend, encore mouillé. Sur la poutre, un clou brille, trop haut. Sur la marche, le vent pousse déjà. On commence où, pour le fil ?</t>
+          <t>La ficelle voyage déjà dans le panier. Dehors, le fil peut aller en trois coins. Un linge mouillé barre encore l'étendoir. Plus haut, un clou attend sur la poutre. Plus bas, le vent pousse la marche. On commence où, pour le fil ?</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -12223,9 +12226,10 @@
       <c r="AW63" t="inlineStr">
         <is>
           <t>narrateur|La ficelle voyage déjà dans le panier.
-narrateur|Sous l'étendoir, un linge pend, encore mouillé.
-narrateur|Sur la poutre, un clou brille, trop haut.
-narrateur|Sur la marche, le vent pousse déjà.
+narrateur|Dehors, le fil peut aller en trois coins.
+narrateur|Un linge mouillé barre encore l'étendoir.
+narrateur|Plus haut, un clou attend sur la poutre.
+narrateur|Plus bas, le vent pousse la marche.
 papa|On commence où, pour le fil ?</t>
         </is>
       </c>
@@ -12970,12 +12974,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Pour toi. Sarah tend la cuillère vers Aniss. Aniss lève le torchon avec la ficelle. Le bois redevient libre, tout doux. Il passe ! Le fil a pris le bord, tout seul. Le métal a trouvé le linge. La ficelle reste un instant sur le bois.</t>
+          <t>Pour toi. Sarah tend la cuillère vers Aniss. Aniss lève le torchon avec la cuillère. La ficelle attend près du bois, déjà. Le bois redevient libre, tout doux. Il passe ! Le fil a pris le bord, tout seul. Le métal a trouvé le linge.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Pour toi. Sarah tend la cuillère vers Aniss. Aniss lève le torchon avec la ficelle. Le bois redevient libre, tout doux. Il passe ! Le fil a pris le bord, tout seul. Le métal a trouvé le linge. La ficelle reste un instant sur le bois.</t>
+          <t>Pour toi. Sarah tend la cuillère vers Aniss. Aniss lève le torchon avec la cuillère. La ficelle attend près du bois, déjà. Le bois redevient libre, tout doux. Il passe ! Le fil a pris le bord, tout seul. Le métal a trouvé le linge.</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -13112,12 +13116,12 @@
         <is>
           <t>enfant-f|Pour toi.
 narrateur|Sarah tend la cuillère vers Aniss.
-narrateur|Aniss lève le torchon avec la ficelle.
+narrateur|Aniss lève le torchon avec la cuillère.
+narrateur|La ficelle attend près du bois, déjà.
 narrateur|Le bois redevient libre, tout doux.
 enfant-f|Il passe !
 maman|Le fil a pris le bord, tout seul.
-papa|Le métal a trouvé le linge.
-narrateur|La ficelle reste un instant sur le bois.</t>
+papa|Le métal a trouvé le linge.</t>
         </is>
       </c>
     </row>
@@ -16483,7 +16487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16526,6 +16530,13 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
